--- a/artfynd/A 37183-2026 artfynd.xlsx
+++ b/artfynd/A 37183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348996</v>
       </c>
       <c r="B2" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37183-2026 artfynd.xlsx
+++ b/artfynd/A 37183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348996</v>
       </c>
       <c r="B2" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37183-2026 artfynd.xlsx
+++ b/artfynd/A 37183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348996</v>
       </c>
       <c r="B2" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136348997</v>
       </c>
       <c r="B3" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136348998</v>
       </c>
       <c r="B4" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136348999</v>
       </c>
       <c r="B5" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37183-2026 artfynd.xlsx
+++ b/artfynd/A 37183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348996</v>
       </c>
       <c r="B2" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37183-2026 artfynd.xlsx
+++ b/artfynd/A 37183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348996</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136348997</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136348998</v>
       </c>
       <c r="B4" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136348999</v>
       </c>
       <c r="B5" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37183-2026 artfynd.xlsx
+++ b/artfynd/A 37183-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348996</v>
       </c>
       <c r="B2" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136348997</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136348998</v>
       </c>
       <c r="B4" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136348999</v>
       </c>
       <c r="B5" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
